--- a/03_Group_comparisons/Proteome_clusters/c_data/04_module_contrasts_all_inputs.xlsx
+++ b/03_Group_comparisons/Proteome_clusters/c_data/04_module_contrasts_all_inputs.xlsx
@@ -332,31 +332,31 @@
     <t>03_Group_comparisons/Proteome_T1/c_data/04_module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>178bb6f90753bf46e952df13cd6e52da</t>
+    <t>71e23f0cfa641728cf1e29896b966d5f</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_T2/c_data/04_module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>380a19762e8f423a5d6bdb1dab1d1c55</t>
+    <t>c353fc363604fb843009364e15b7b0d3</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_T3/c_data/04_module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>9a98f81ea2be2ee9b1c239ea09c52e33</t>
+    <t>f9a821b1c778d38d658ca49054e0a257</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_training/c_data/04_module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>9cb2299862b8bbc3f6849e49e8783418</t>
+    <t>5ed71d533f404f8c55e600b32a2b6dd9</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_acute/c_data/04_module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>d43c100aca8cab22e5c0bcccc443aab1</t>
+    <t>a07945bb572e3e13d02c749e1a3feadb</t>
   </si>
   <si>
     <t>BiocGenerics</t>
